--- a/public/exports-60-250/29189986.xlsx
+++ b/public/exports-60-250/29189986.xlsx
@@ -5389,12 +5389,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289828</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
